--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B560C8A8-E80A-4B46-A2C8-DC80CBA4A828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25688E6-57FF-469E-A4AF-5567012B5D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25688E6-57FF-469E-A4AF-5567012B5D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638A0DAC-1EB5-4BC8-8D6A-08EE8C22A52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638A0DAC-1EB5-4BC8-8D6A-08EE8C22A52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946081D5-9476-4FD0-A805-B991D9067A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946081D5-9476-4FD0-A805-B991D9067A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3763E5EF-F0F3-4244-9DB8-93A48B4091F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3763E5EF-F0F3-4244-9DB8-93A48B4091F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9032395B-1B8A-4A8C-8375-CACB9DA11F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9032395B-1B8A-4A8C-8375-CACB9DA11F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC486DA-8A20-4BE1-9782-25650B455B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC486DA-8A20-4BE1-9782-25650B455B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2913C4CB-8AD2-4A46-966C-90D06CFFB99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="435" windowWidth="27885" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2913C4CB-8AD2-4A46-966C-90D06CFFB99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC75D9-45D9-494A-B5D7-349AC2D9D55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC75D9-45D9-494A-B5D7-349AC2D9D55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504601DE-EB81-47AB-9427-61D46F7F5104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504601DE-EB81-47AB-9427-61D46F7F5104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D45A430-8A37-448C-AC74-C01927015C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D45A430-8A37-448C-AC74-C01927015C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A482A8-3E85-4EC8-8D04-D8576F026DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A482A8-3E85-4EC8-8D04-D8576F026DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A3991D-33B5-45B1-92A6-5182A28A896E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A3991D-33B5-45B1-92A6-5182A28A896E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF21E96-67C1-4921-B2D5-8A7944FAAD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF21E96-67C1-4921-B2D5-8A7944FAAD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49854A22-A4C5-4715-9478-CB09FBB8E0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49854A22-A4C5-4715-9478-CB09FBB8E0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBEE9D9-D453-434D-9E13-F744DCF562A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBEE9D9-D453-434D-9E13-F744DCF562A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8320127-14C4-4A4E-BDA1-B99644CBB74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8320127-14C4-4A4E-BDA1-B99644CBB74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9530E8-D324-4334-BCF2-B76796F57883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9530E8-D324-4334-BCF2-B76796F57883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80370688-1398-42EF-B816-A12C9D96D321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80370688-1398-42EF-B816-A12C9D96D321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583D4257-839D-4B9D-B694-D14833FA3C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583D4257-839D-4B9D-B694-D14833FA3C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8219D8D4-F932-47B3-98FD-3C438B9FD0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8219D8D4-F932-47B3-98FD-3C438B9FD0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DAD9D3-498F-4229-83C5-C267F8E66783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DAD9D3-498F-4229-83C5-C267F8E66783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7923DABB-0AA7-4AFF-9472-A502146C2C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7923DABB-0AA7-4AFF-9472-A502146C2C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD00987C-CB97-4C2A-9F87-36E6111CEF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD00987C-CB97-4C2A-9F87-36E6111CEF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389F9791-EFA9-4A5A-9352-8E7B8F283FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389F9791-EFA9-4A5A-9352-8E7B8F283FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B213E6-B2F4-4C70-9ACD-AFC38F1D7D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B213E6-B2F4-4C70-9ACD-AFC38F1D7D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497DF066-FB28-4A89-BFEC-0BB6781C0BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497DF066-FB28-4A89-BFEC-0BB6781C0BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A82137F-DB82-42CE-BFEA-F433522A3F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A82137F-DB82-42CE-BFEA-F433522A3F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43E864E-2960-4136-B49E-5D26887E4979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43E864E-2960-4136-B49E-5D26887E4979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB3C0BB-493C-491F-8367-F59CB07C5968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB3C0BB-493C-491F-8367-F59CB07C5968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B2E8D4-CBFE-4B2B-BCFE-054FB846F5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B2E8D4-CBFE-4B2B-BCFE-054FB846F5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508A4386-36CA-4938-9F7F-334B25E1E80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508A4386-36CA-4938-9F7F-334B25E1E80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE626D1D-306C-4948-B090-950CFB4D0DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE626D1D-306C-4948-B090-950CFB4D0DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F6D7D0-D081-4139-8E58-583DFA2F6CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F6D7D0-D081-4139-8E58-583DFA2F6CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04A75DE-F0FD-4FF6-AA91-39322C0753BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04A75DE-F0FD-4FF6-AA91-39322C0753BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB81A2A-AABD-4DC3-BA53-DAC3A0244079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB81A2A-AABD-4DC3-BA53-DAC3A0244079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861B6D55-31F6-467D-8A30-C1CBB4A1B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861B6D55-31F6-467D-8A30-C1CBB4A1B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AF0E0C-09E3-4A51-A2EF-95DAA2560343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AF0E0C-09E3-4A51-A2EF-95DAA2560343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFF83A6-37D3-4F50-946A-A43973B746DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFF83A6-37D3-4F50-946A-A43973B746DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99E8ECC-4DC3-4AD8-AAF1-53F5C7F79689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99E8ECC-4DC3-4AD8-AAF1-53F5C7F79689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F40FD1-EFCF-4201-8C2B-E6072E3CA957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F40FD1-EFCF-4201-8C2B-E6072E3CA957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04852A9B-8534-4532-A208-D39F2E72218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04852A9B-8534-4532-A208-D39F2E72218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEEF23B-8740-44E4-89C2-FE8E6F582D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEEF23B-8740-44E4-89C2-FE8E6F582D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B363567E-ABB4-47F1-A89D-4BE2E550DEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B363567E-ABB4-47F1-A89D-4BE2E550DEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE476311-6D1B-4E54-B872-FC5CB241CC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE476311-6D1B-4E54-B872-FC5CB241CC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2E6636-89FF-4528-A884-CEC0EEAE9E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2E6636-89FF-4528-A884-CEC0EEAE9E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870DE28F-EEBA-4299-8D26-35F2BB37808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870DE28F-EEBA-4299-8D26-35F2BB37808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95415D02-EF53-4DE2-B9FE-D08BCBC8AD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95415D02-EF53-4DE2-B9FE-D08BCBC8AD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D204C-92B3-4FF0-8B28-53159DDB69F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D204C-92B3-4FF0-8B28-53159DDB69F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E9ABF7-182F-490A-9785-7C58747CC9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E9ABF7-182F-490A-9785-7C58747CC9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F313726F-8B82-424D-9D3F-19421721936F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F313726F-8B82-424D-9D3F-19421721936F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9971EB-F999-4E25-9B08-19C1C7853914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9971EB-F999-4E25-9B08-19C1C7853914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E706C7-1B81-4AC3-8ECD-41F63573CDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E706C7-1B81-4AC3-8ECD-41F63573CDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E6C05-7F08-48C8-ADB4-2A04D01E61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E6C05-7F08-48C8-ADB4-2A04D01E61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E417CCC-F697-481A-B786-5018D6D01E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E417CCC-F697-481A-B786-5018D6D01E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAEC414-98EA-4A3E-8CF4-ECCB8F558F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAEC414-98EA-4A3E-8CF4-ECCB8F558F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9129BA4-040F-4296-A163-10D78752EC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9129BA4-040F-4296-A163-10D78752EC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57910D28-24C4-4D7F-8AF5-2DD4765F93E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57910D28-24C4-4D7F-8AF5-2DD4765F93E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A67A2C8-56F8-48B3-B472-9187D62520F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D607911-6232-4223-A8E4-CAEE9897DDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DC240F-3102-48CB-B58D-33E61486FD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DC240F-3102-48CB-B58D-33E61486FD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E5F70C-D47B-432B-B160-6C419B3BDE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E5F70C-D47B-432B-B160-6C419B3BDE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD07698-5304-483A-B45B-79C291C82E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD07698-5304-483A-B45B-79C291C82E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51783C8-BE08-4041-B3EE-C28B09EBE084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51783C8-BE08-4041-B3EE-C28B09EBE084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3529680-B823-448D-B268-ED668AFF6E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3529680-B823-448D-B268-ED668AFF6E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A55CB72-DC9F-426A-9035-83ACA707FED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A55CB72-DC9F-426A-9035-83ACA707FED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8C427D-2D7D-463C-9EDF-AD7EE552AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8C427D-2D7D-463C-9EDF-AD7EE552AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFB5B46-F495-4C1D-A1F6-8C192A562E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFB5B46-F495-4C1D-A1F6-8C192A562E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107226EF-6CA6-4576-8D20-37D0B4EB74D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107226EF-6CA6-4576-8D20-37D0B4EB74D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5E3B1A-72CF-498F-965E-199043376951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5E3B1A-72CF-498F-965E-199043376951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446CE619-0591-4C4D-8721-DCBAC0E3EEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446CE619-0591-4C4D-8721-DCBAC0E3EEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29193023-4DEF-49D7-B60C-6B7F61A4545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29193023-4DEF-49D7-B60C-6B7F61A4545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877673E9-53CF-48CE-BC1F-31258920F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877673E9-53CF-48CE-BC1F-31258920F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6908A6-C8DE-4A8E-A302-C1861C079406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6908A6-C8DE-4A8E-A302-C1861C079406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC3950-7C2D-4391-9921-3C2BABB475CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC3950-7C2D-4391-9921-3C2BABB475CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC0DF8-56E0-4E79-9C13-BFEB656158E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC0DF8-56E0-4E79-9C13-BFEB656158E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979214BA-4719-4A50-B01D-AA20C3519082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979214BA-4719-4A50-B01D-AA20C3519082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D560660F-4F9F-4E08-B3BE-17B37F180932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D560660F-4F9F-4E08-B3BE-17B37F180932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88B28AA-0029-429F-9C81-8EE3B338EB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88B28AA-0029-429F-9C81-8EE3B338EB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28CD91F-C3AD-43A1-9924-C8BB44D24BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28CD91F-C3AD-43A1-9924-C8BB44D24BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAE1BFB-863C-4733-B4B6-6CC7A77E14E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAE1BFB-863C-4733-B4B6-6CC7A77E14E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BCAE48-7CD2-45A1-A239-ACC01E143A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BCAE48-7CD2-45A1-A239-ACC01E143A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C271C1CC-CB3C-48FC-86CB-20F34F1E3E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C271C1CC-CB3C-48FC-86CB-20F34F1E3E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA75422-8EEF-4529-A4B5-3AA17F30DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA75422-8EEF-4529-A4B5-3AA17F30DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B603DD-24FF-48B5-BB91-9C755BD9BF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B603DD-24FF-48B5-BB91-9C755BD9BF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180AF479-01ED-4759-9558-1F87F66D6B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180AF479-01ED-4759-9558-1F87F66D6B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B229142D-844A-477F-8527-D7B58B1021E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B229142D-844A-477F-8527-D7B58B1021E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED6F2A1-2D0E-47F5-92FA-B7278ABF6E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED6F2A1-2D0E-47F5-92FA-B7278ABF6E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60B159F-5A9A-4879-BEF4-BBFDB384360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="3795" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60B159F-5A9A-4879-BEF4-BBFDB384360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3D5956-A28C-41D1-94FE-D803E8DE6700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1305" yWindow="3795" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3D5956-A28C-41D1-94FE-D803E8DE6700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1364E3F-DA6A-480C-9E2B-F69F70D856C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1305" yWindow="3795" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1364E3F-DA6A-480C-9E2B-F69F70D856C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E72F24C-F8E3-411C-BD80-8DBF6353E8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="3795" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E72F24C-F8E3-411C-BD80-8DBF6353E8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94CC70C-C3FC-45B7-BF3B-F60C2B2A7456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94CC70C-C3FC-45B7-BF3B-F60C2B2A7456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B468E1D2-9F06-4021-92A8-9AB2B0276CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B468E1D2-9F06-4021-92A8-9AB2B0276CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56948CAB-43C2-4D4B-8618-015AAF111FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56948CAB-43C2-4D4B-8618-015AAF111FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184026CB-471E-4509-A854-BD3878D26C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184026CB-471E-4509-A854-BD3878D26C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="4485" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184026CB-471E-4509-A854-BD3878D26C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="4485" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184026CB-471E-4509-A854-BD3878D26C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="4500" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/btl_istruzioni.xlsx
+++ b/btl_istruzioni.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184026CB-471E-4509-A854-BD3878D26C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="4500" windowWidth="22935" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
